--- a/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6777DA-E2CA-4C73-9DEE-83BDB34E8655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08436F1B-A52A-4CB0-967B-7C4DE1504E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0972039C-DF36-4EBB-80B7-4B19A7AF5822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E61A712-6B67-4D64-B92F-C88BA2B15024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="472">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -1238,6 +1251,204 @@
   </si>
   <si>
     <t>Ristorante Aroma</t>
+  </si>
+  <si>
+    <t>Alyan’s Middle Eastern &amp; Mediterranean Restaurant</t>
+  </si>
+  <si>
+    <t>603 S 4th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 922-3553  </t>
+  </si>
+  <si>
+    <t>Apricot Stone</t>
+  </si>
+  <si>
+    <t>428 W Girard Ave, Philadelphia, PA 19123 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 606-6596  </t>
+  </si>
+  <si>
+    <t>1247 S 13th St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 465-2200  </t>
+  </si>
+  <si>
+    <t>Casablanca Mediterranean Grill</t>
+  </si>
+  <si>
+    <t>947 Federal St, Philadelphia, PA 19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 324-5165  </t>
+  </si>
+  <si>
+    <t>Chabba Thai bistro</t>
+  </si>
+  <si>
+    <t>4343 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 483-1979  </t>
+  </si>
+  <si>
+    <t>Fiorino</t>
+  </si>
+  <si>
+    <t>3572 Indian Queen Ln, Philadelphia, PA 19129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 843-1500  </t>
+  </si>
+  <si>
+    <t>Han dynasty (manayunk)</t>
+  </si>
+  <si>
+    <t>4356 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 508-2066  </t>
+  </si>
+  <si>
+    <t>June BYOB</t>
+  </si>
+  <si>
+    <t> 690 Haddon Ave, Collingswood, NJ 08108 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(856) 240-7041  </t>
+  </si>
+  <si>
+    <t>Kung Fu Hot Pot</t>
+  </si>
+  <si>
+    <t>1008 Cherry St 3rd floor, Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 606-1899  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 928-3262  </t>
+  </si>
+  <si>
+    <t>Sakartvelo</t>
+  </si>
+  <si>
+    <t>705 Chestnut St, Philadelphia, PA 19106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 319-1631  </t>
+  </si>
+  <si>
+    <t>Scampi</t>
+  </si>
+  <si>
+    <t> 617 S 3rd St, Philadelphia, PA 19147 </t>
+  </si>
+  <si>
+    <t>Vientiane Bistro</t>
+  </si>
+  <si>
+    <t>2537 Kensington Ave, Philadelphia, PA 19125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 703-8199  </t>
+  </si>
+  <si>
+    <t>White yak</t>
+  </si>
+  <si>
+    <t> 6118 Ridge Ave, Philadelphia, PA 19128 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 483-0764  </t>
+  </si>
+  <si>
+    <t>Yamitsuki</t>
+  </si>
+  <si>
+    <t>1028 Arch St , Philadelphia, PA 19107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(215) 629-3888  </t>
+  </si>
+  <si>
+    <t>Yanako restaurant</t>
+  </si>
+  <si>
+    <t>4345 Main St, Philadelphia, PA 19127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(267) 297-8151  </t>
+  </si>
+  <si>
+    <t>Zeppoli</t>
+  </si>
+  <si>
+    <t>618 Collings Ave, Collingswood NJ 08107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(856) 854-2670  </t>
+  </si>
+  <si>
+    <t>https://www.scampiphilly.com/menu</t>
+  </si>
+  <si>
+    <t>http://www.junebyob.com/</t>
+  </si>
+  <si>
+    <t>http://www.zeppolirestaurant.com/</t>
+  </si>
+  <si>
+    <t>http://www.casablanca-grill.com/</t>
+  </si>
+  <si>
+    <t>https://www.fiorino.us/</t>
+  </si>
+  <si>
+    <t>http://www.handynasty.net/</t>
+  </si>
+  <si>
+    <t>https://whiteyakrestaurant.com/?utm_source=google</t>
+  </si>
+  <si>
+    <t>https://www.vientianebistro.com/</t>
+  </si>
+  <si>
+    <t>https://theyanako.com/</t>
+  </si>
+  <si>
+    <t>https://chabaathai.com/</t>
+  </si>
+  <si>
+    <t>http://www.apricotstonephilly.com/</t>
+  </si>
+  <si>
+    <t>https://sakartvelopa.com/</t>
+  </si>
+  <si>
+    <t>https://yamitsuki1028.wixsite.com/yamitsukiramen</t>
+  </si>
+  <si>
+    <t>info@junebyob.com</t>
+  </si>
+  <si>
+    <t>casablancamg947@gmail.com</t>
+  </si>
+  <si>
+    <t>treley@whiteyakrestaurant.com</t>
+  </si>
+  <si>
+    <t>astigma@astigmatic.com</t>
+  </si>
+  <si>
+    <t>info@apricotstonephilly.com</t>
+  </si>
+  <si>
+    <t>yamitsuki1028@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1456,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1310,7 +1521,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1613,10 +1824,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S73"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="21.125" customWidth="1"/>
+    <col min="9" max="9" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1703,7 +1916,7 @@
       <c r="H2">
         <v>-75.1753073</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J2" t="s">
@@ -1735,7 +1948,7 @@
       <c r="H3">
         <v>-75.152359599999997</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1764,7 +1977,7 @@
       <c r="H4">
         <v>-75.179640800000001</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1790,7 +2003,7 @@
       <c r="H5">
         <v>-75.170259099999996</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J5" t="s">
@@ -1822,7 +2035,7 @@
       <c r="H6">
         <v>-75.165249199999991</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J6" t="s">
@@ -1857,7 +2070,7 @@
       <c r="H7">
         <v>-75.144517199999996</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J7" t="s">
@@ -1889,7 +2102,7 @@
       <c r="H8">
         <v>-75.141018599999995</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J8" t="s">
@@ -1921,7 +2134,7 @@
       <c r="H9">
         <v>-75.161606300000003</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J9" t="s">
@@ -1950,7 +2163,7 @@
       <c r="H10">
         <v>-75.129705099999995</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J10" t="s">
@@ -1982,7 +2195,7 @@
       <c r="H11">
         <v>-75.164066699999992</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2011,7 +2224,7 @@
       <c r="H12">
         <v>-75.164232699999999</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2040,7 +2253,7 @@
       <c r="H13">
         <v>-75.144519399999993</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2069,7 +2282,7 @@
       <c r="H14">
         <v>-75.140985200000003</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J14" t="s">
@@ -2098,7 +2311,7 @@
       <c r="H15">
         <v>-75.180016899999998</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J15" t="s">
@@ -2130,7 +2343,7 @@
       <c r="H16">
         <v>-75.170737899999992</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2156,7 +2369,7 @@
       <c r="H17">
         <v>-75.160454999999999</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2185,7 +2398,7 @@
       <c r="H18">
         <v>-75.160108000000008</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2211,7 +2424,7 @@
       <c r="H19">
         <v>-75.134557399999991</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2240,7 +2453,7 @@
       <c r="H20">
         <v>-75.146249400000002</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2269,7 +2482,7 @@
       <c r="H21">
         <v>-75.167785299999991</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2295,7 +2508,7 @@
       <c r="H22">
         <v>-75.171386099999992</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2324,7 +2537,7 @@
       <c r="H23">
         <v>-75.171194099999994</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2350,7 +2563,7 @@
       <c r="H24">
         <v>-75.152963700000001</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J24" t="s">
@@ -2382,7 +2595,7 @@
       <c r="H25">
         <v>-75.173786499999991</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J25" t="s">
@@ -2414,7 +2627,7 @@
       <c r="H26">
         <v>-75.157853799999998</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2443,7 +2656,7 @@
       <c r="H27">
         <v>-75.174123500000007</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
@@ -2475,7 +2688,7 @@
       <c r="H28">
         <v>-75.161768199999997</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J28" t="s">
@@ -2510,7 +2723,7 @@
       <c r="H29">
         <v>-75.160984799999994</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2539,7 +2752,7 @@
       <c r="H30">
         <v>-75.170019699999997</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2568,7 +2781,7 @@
       <c r="H31">
         <v>-75.144386900000001</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J31" t="s">
@@ -2600,7 +2813,7 @@
       <c r="H32">
         <v>-75.156515900000002</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J32" t="s">
@@ -2632,7 +2845,7 @@
       <c r="H33">
         <v>-75.140709299999997</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J33" t="s">
@@ -2661,7 +2874,7 @@
       <c r="H34">
         <v>-75.175115599999998</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2690,7 +2903,7 @@
       <c r="H35">
         <v>-75.167463699999999</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2716,7 +2929,7 @@
       <c r="H36">
         <v>-75.16734799999999</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2745,7 +2958,7 @@
       <c r="H37">
         <v>-75.171119699999991</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2774,7 +2987,7 @@
       <c r="H38">
         <v>-75.174716699999991</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J38" t="s">
@@ -2806,7 +3019,7 @@
       <c r="H39">
         <v>-75.155556500000003</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2835,7 +3048,7 @@
       <c r="H40">
         <v>-75.185306799999992</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J40" t="s">
@@ -2867,7 +3080,7 @@
       <c r="H41">
         <v>-75.177968399999997</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="J41" t="s">
@@ -2899,7 +3112,7 @@
       <c r="H42">
         <v>-75.174830900000003</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2928,7 +3141,7 @@
       <c r="H43">
         <v>-75.217944799999998</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2957,7 +3170,7 @@
       <c r="H44">
         <v>-75.149544399999996</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -2983,7 +3196,7 @@
       <c r="H45">
         <v>-75.050069499999992</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3009,7 +3222,7 @@
       <c r="H46">
         <v>-75.154025899999993</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J46" t="s">
@@ -3041,7 +3254,7 @@
       <c r="H47">
         <v>-75.149088399999997</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3067,7 +3280,7 @@
       <c r="H48">
         <v>-75.156259599999998</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3096,7 +3309,7 @@
       <c r="H49">
         <v>-75.178519699999995</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3125,7 +3338,7 @@
       <c r="H50">
         <v>-75.150354600000014</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J50" t="s">
@@ -3160,7 +3373,7 @@
       <c r="H51">
         <v>-75.034327399999995</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3186,7 +3399,7 @@
       <c r="H52">
         <v>-75.171258600000002</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3209,7 +3422,7 @@
       <c r="H53">
         <v>-75.173383200000004</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3238,7 +3451,7 @@
       <c r="H54">
         <v>-75.157960899999992</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J54" t="s">
@@ -3273,7 +3486,7 @@
       <c r="H55">
         <v>-75.153989299999992</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3302,7 +3515,7 @@
       <c r="H56">
         <v>-75.16970049999999</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J56" t="s">
@@ -3331,7 +3544,7 @@
       <c r="H57">
         <v>-75.169153299999991</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3360,7 +3573,7 @@
       <c r="H58">
         <v>-75.190036300000003</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J58" t="s">
@@ -3398,7 +3611,7 @@
       <c r="H59">
         <v>-75.163266499999992</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J59" t="s">
@@ -3430,7 +3643,7 @@
       <c r="H60">
         <v>-75.157535600000003</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3459,7 +3672,7 @@
       <c r="H61">
         <v>-75.172149099999999</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J61" t="s">
@@ -3491,7 +3704,7 @@
       <c r="H62">
         <v>-75.102839599999996</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J62" t="s">
@@ -3523,7 +3736,7 @@
       <c r="H63">
         <v>-75.146044199999992</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="2" t="s">
         <v>246</v>
       </c>
     </row>
@@ -3552,7 +3765,7 @@
       <c r="H64">
         <v>-75.159783899999994</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="2" t="s">
         <v>246</v>
       </c>
       <c r="J64" t="s">
@@ -3562,7 +3775,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1747</v>
       </c>
@@ -3587,11 +3800,11 @@
       <c r="H65">
         <v>-75.113133699999992</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1748</v>
       </c>
@@ -3616,11 +3829,11 @@
       <c r="H66">
         <v>-75.147412399999993</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1749</v>
       </c>
@@ -3645,11 +3858,11 @@
       <c r="H67">
         <v>-75.174111199999999</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1750</v>
       </c>
@@ -3674,11 +3887,11 @@
       <c r="H68">
         <v>-75.160342099999994</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1754</v>
       </c>
@@ -3703,14 +3916,14 @@
       <c r="H69">
         <v>-75.177395099999998</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="2" t="s">
         <v>380</v>
       </c>
       <c r="J69" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1755</v>
       </c>
@@ -3732,14 +3945,14 @@
       <c r="H70">
         <v>-75.182546800000011</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="2" t="s">
         <v>380</v>
       </c>
       <c r="J70" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1756</v>
       </c>
@@ -3764,14 +3977,14 @@
       <c r="H71">
         <v>-75.129835499999999</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="2" t="s">
         <v>380</v>
       </c>
       <c r="J71" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1757</v>
       </c>
@@ -3796,14 +4009,14 @@
       <c r="H72">
         <v>-75.160762800000001</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="2" t="s">
         <v>398</v>
       </c>
       <c r="J72" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1402</v>
       </c>
@@ -3830,6 +4043,463 @@
       </c>
       <c r="I73" s="2">
         <v>45985</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1408</v>
+      </c>
+      <c r="B74" t="s">
+        <v>406</v>
+      </c>
+      <c r="C74" t="s">
+        <v>407</v>
+      </c>
+      <c r="D74" t="s">
+        <v>408</v>
+      </c>
+      <c r="G74">
+        <v>39.941414799999997</v>
+      </c>
+      <c r="H74">
+        <v>-75.149054199999995</v>
+      </c>
+      <c r="I74" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>1389</v>
+      </c>
+      <c r="B75" t="s">
+        <v>409</v>
+      </c>
+      <c r="C75" t="s">
+        <v>410</v>
+      </c>
+      <c r="D75" t="s">
+        <v>411</v>
+      </c>
+      <c r="E75" t="s">
+        <v>463</v>
+      </c>
+      <c r="G75">
+        <v>39.969888599999997</v>
+      </c>
+      <c r="H75">
+        <v>-75.144038499999994</v>
+      </c>
+      <c r="I75" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J75" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>1374</v>
+      </c>
+      <c r="B76" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s">
+        <v>412</v>
+      </c>
+      <c r="D76" t="s">
+        <v>413</v>
+      </c>
+      <c r="E76" t="s">
+        <v>44</v>
+      </c>
+      <c r="G76">
+        <v>39.933934299999997</v>
+      </c>
+      <c r="H76">
+        <v>-75.165249199999991</v>
+      </c>
+      <c r="I76" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J76" t="s">
+        <v>47</v>
+      </c>
+      <c r="K76" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>1407</v>
+      </c>
+      <c r="B77" t="s">
+        <v>414</v>
+      </c>
+      <c r="C77" t="s">
+        <v>415</v>
+      </c>
+      <c r="D77" t="s">
+        <v>416</v>
+      </c>
+      <c r="E77" t="s">
+        <v>456</v>
+      </c>
+      <c r="G77">
+        <v>39.9346672</v>
+      </c>
+      <c r="H77">
+        <v>-75.160286099999993</v>
+      </c>
+      <c r="I77" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J77" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>1398</v>
+      </c>
+      <c r="B78" t="s">
+        <v>417</v>
+      </c>
+      <c r="C78" t="s">
+        <v>418</v>
+      </c>
+      <c r="D78" t="s">
+        <v>419</v>
+      </c>
+      <c r="E78" t="s">
+        <v>462</v>
+      </c>
+      <c r="G78">
+        <v>40.025693400000002</v>
+      </c>
+      <c r="H78">
+        <v>-75.2233971</v>
+      </c>
+      <c r="I78" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>1401</v>
+      </c>
+      <c r="B79" t="s">
+        <v>420</v>
+      </c>
+      <c r="C79" t="s">
+        <v>421</v>
+      </c>
+      <c r="D79" t="s">
+        <v>422</v>
+      </c>
+      <c r="E79" t="s">
+        <v>457</v>
+      </c>
+      <c r="G79">
+        <v>40.009791999999997</v>
+      </c>
+      <c r="H79">
+        <v>-75.190426099999996</v>
+      </c>
+      <c r="I79" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>1404</v>
+      </c>
+      <c r="B80" t="s">
+        <v>423</v>
+      </c>
+      <c r="C80" t="s">
+        <v>424</v>
+      </c>
+      <c r="D80" t="s">
+        <v>425</v>
+      </c>
+      <c r="E80" t="s">
+        <v>458</v>
+      </c>
+      <c r="G80">
+        <v>40.025373700000003</v>
+      </c>
+      <c r="H80">
+        <v>-75.223862799999992</v>
+      </c>
+      <c r="I80" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>1410</v>
+      </c>
+      <c r="B81" t="s">
+        <v>426</v>
+      </c>
+      <c r="C81" t="s">
+        <v>427</v>
+      </c>
+      <c r="D81" t="s">
+        <v>428</v>
+      </c>
+      <c r="E81" t="s">
+        <v>454</v>
+      </c>
+      <c r="G81">
+        <v>39.916215800000003</v>
+      </c>
+      <c r="H81">
+        <v>-75.069438599999998</v>
+      </c>
+      <c r="I81" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J81" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>1417</v>
+      </c>
+      <c r="B82" t="s">
+        <v>429</v>
+      </c>
+      <c r="C82" t="s">
+        <v>430</v>
+      </c>
+      <c r="D82" t="s">
+        <v>431</v>
+      </c>
+      <c r="G82">
+        <v>39.954462199999988</v>
+      </c>
+      <c r="H82">
+        <v>-75.156541500000003</v>
+      </c>
+      <c r="I82" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>1377</v>
+      </c>
+      <c r="B83" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" t="s">
+        <v>115</v>
+      </c>
+      <c r="D83" t="s">
+        <v>432</v>
+      </c>
+      <c r="E83" t="s">
+        <v>117</v>
+      </c>
+      <c r="G83">
+        <v>39.941107500000001</v>
+      </c>
+      <c r="H83">
+        <v>-75.146249400000002</v>
+      </c>
+      <c r="I83" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>1388</v>
+      </c>
+      <c r="B84" t="s">
+        <v>433</v>
+      </c>
+      <c r="C84" t="s">
+        <v>434</v>
+      </c>
+      <c r="D84" t="s">
+        <v>435</v>
+      </c>
+      <c r="E84" t="s">
+        <v>464</v>
+      </c>
+      <c r="G84">
+        <v>39.949672</v>
+      </c>
+      <c r="H84">
+        <v>-75.152562000000017</v>
+      </c>
+      <c r="I84" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>1412</v>
+      </c>
+      <c r="B85" t="s">
+        <v>436</v>
+      </c>
+      <c r="C85" t="s">
+        <v>437</v>
+      </c>
+      <c r="E85" t="s">
+        <v>453</v>
+      </c>
+      <c r="G85">
+        <v>39.940898199999999</v>
+      </c>
+      <c r="H85">
+        <v>-75.147503599999993</v>
+      </c>
+      <c r="I85" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>1383</v>
+      </c>
+      <c r="B86" t="s">
+        <v>438</v>
+      </c>
+      <c r="C86" t="s">
+        <v>439</v>
+      </c>
+      <c r="D86" t="s">
+        <v>440</v>
+      </c>
+      <c r="E86" t="s">
+        <v>460</v>
+      </c>
+      <c r="G86">
+        <v>39.988109899999998</v>
+      </c>
+      <c r="H86">
+        <v>-75.1282341</v>
+      </c>
+      <c r="I86" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J86" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1376</v>
+      </c>
+      <c r="B87" t="s">
+        <v>441</v>
+      </c>
+      <c r="C87" t="s">
+        <v>442</v>
+      </c>
+      <c r="D87" t="s">
+        <v>443</v>
+      </c>
+      <c r="E87" t="s">
+        <v>459</v>
+      </c>
+      <c r="G87">
+        <v>40.033780200000002</v>
+      </c>
+      <c r="H87">
+        <v>-75.21579659999999</v>
+      </c>
+      <c r="I87" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J87" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>1387</v>
+      </c>
+      <c r="B88" t="s">
+        <v>444</v>
+      </c>
+      <c r="C88" t="s">
+        <v>445</v>
+      </c>
+      <c r="D88" t="s">
+        <v>446</v>
+      </c>
+      <c r="E88" t="s">
+        <v>465</v>
+      </c>
+      <c r="G88">
+        <v>39.953542300000002</v>
+      </c>
+      <c r="H88">
+        <v>-75.157455200000001</v>
+      </c>
+      <c r="I88" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J88" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>1399</v>
+      </c>
+      <c r="B89" t="s">
+        <v>447</v>
+      </c>
+      <c r="C89" t="s">
+        <v>448</v>
+      </c>
+      <c r="D89" t="s">
+        <v>449</v>
+      </c>
+      <c r="E89" t="s">
+        <v>461</v>
+      </c>
+      <c r="G89">
+        <v>40.025600900000001</v>
+      </c>
+      <c r="H89">
+        <v>-75.2234981</v>
+      </c>
+      <c r="I89" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>1409</v>
+      </c>
+      <c r="B90" t="s">
+        <v>450</v>
+      </c>
+      <c r="C90" t="s">
+        <v>451</v>
+      </c>
+      <c r="D90" t="s">
+        <v>452</v>
+      </c>
+      <c r="E90" t="s">
+        <v>455</v>
+      </c>
+      <c r="G90">
+        <v>39.910713899999998</v>
+      </c>
+      <c r="H90">
+        <v>-75.084474200000002</v>
+      </c>
+      <c r="I90" s="2">
+        <v>45987</v>
       </c>
     </row>
   </sheetData>

--- a/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
+++ b/philly_yelp_crawler/data/Philly BYOB Restaurant_with_websites_merged.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\philly_yelp_crawler\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E61A712-6B67-4D64-B92F-C88BA2B15024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1C3D72-365D-4EB4-8115-150A74B84056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="466">
   <si>
     <t>WP_Post_ID</t>
   </si>
@@ -107,9 +107,6 @@
     <t>https://www.yelp.com/biz/a-mano-philadelphia</t>
   </si>
   <si>
-    <t>2025-11-08</t>
-  </si>
-  <si>
     <t>info@amanophl.com</t>
   </si>
   <si>
@@ -632,21 +629,6 @@
     <t>https://www.yelp.com/biz/rice-and-sambal-philadelphia</t>
   </si>
   <si>
-    <t>Sawatdee</t>
-  </si>
-  <si>
-    <t>534 S 15th St, Philadelphia, PA 19146, United States</t>
-  </si>
-  <si>
-    <t>(215) 790-1299</t>
-  </si>
-  <si>
-    <t>https://www.sawatdeephiladelphia.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/sawatdee-thai-restaurant-philadelphia-2</t>
-  </si>
-  <si>
     <t>Scannicchio's</t>
   </si>
   <si>
@@ -761,6 +743,9 @@
     <t>https://www.yelp.com/biz/vientiane-caf%C3%A9-philadelphia-3</t>
   </si>
   <si>
+    <t>Ristorante Aroma</t>
+  </si>
+  <si>
     <t>1245 S 3rd St, Philadelphia, PA 19147</t>
   </si>
   <si>
@@ -773,9 +758,6 @@
     <t>https://www.yelp.com/biz/ristorante-aroma-philadelphia-3</t>
   </si>
   <si>
-    <t>2025-11-16</t>
-  </si>
-  <si>
     <t>Bricco Coal Fired Pizza</t>
   </si>
   <si>
@@ -788,27 +770,6 @@
     <t>https://www.yelp.com/biz/bricco-coal-fired-pizza-westmont</t>
   </si>
   <si>
-    <t>Buca D'oro Ristorante</t>
-  </si>
-  <si>
-    <t>711 Locust St, Philadelphia, PA 19106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 928-0556  </t>
-  </si>
-  <si>
-    <t>https://bucadororistorante.com/</t>
-  </si>
-  <si>
-    <t>https://www.yelp.com/biz/la-buca-philadelphia</t>
-  </si>
-  <si>
-    <t>john@doe.com</t>
-  </si>
-  <si>
-    <t>bucadoro@hotmail.com</t>
-  </si>
-  <si>
     <t>Cilantro Mediterranean Cuisine</t>
   </si>
   <si>
@@ -1175,9 +1136,6 @@
     <t>https://www.yelp.com/biz/chateau-rouge-philadelphia</t>
   </si>
   <si>
-    <t>2025-11-17</t>
-  </si>
-  <si>
     <t>hello@chateaurougephilly.com</t>
   </si>
   <si>
@@ -1229,9 +1187,6 @@
     <t>https://www.yelp.com/biz/mabu-kitchen-philadelphia</t>
   </si>
   <si>
-    <t>2025-11-18</t>
-  </si>
-  <si>
     <t>mabukitchenmanager@outlook.com</t>
   </si>
   <si>
@@ -1250,9 +1205,6 @@
     <t>https://www.yelp.com/biz/santuccis-original-square-pizza-philadelphia-2</t>
   </si>
   <si>
-    <t>Ristorante Aroma</t>
-  </si>
-  <si>
     <t>Alyan’s Middle Eastern &amp; Mediterranean Restaurant</t>
   </si>
   <si>
@@ -1271,10 +1223,13 @@
     <t xml:space="preserve">(267) 606-6596  </t>
   </si>
   <si>
-    <t>1247 S 13th St, Philadelphia, PA 19147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(215) 465-2200  </t>
+    <t>http://www.apricotstonephilly.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/apricot-stone-philadelphia-4</t>
+  </si>
+  <si>
+    <t>info@apricotstonephilly.com</t>
   </si>
   <si>
     <t>Casablanca Mediterranean Grill</t>
@@ -1286,6 +1241,15 @@
     <t xml:space="preserve">(267) 324-5165  </t>
   </si>
   <si>
+    <t>http://www.casablanca-grill.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/casablanca-mediterranean-grill-philadelphia</t>
+  </si>
+  <si>
+    <t>casablancamg947@gmail.com</t>
+  </si>
+  <si>
     <t>Chabba Thai bistro</t>
   </si>
   <si>
@@ -1295,6 +1259,9 @@
     <t xml:space="preserve">(215) 483-1979  </t>
   </si>
   <si>
+    <t>https://chabaathai.com/</t>
+  </si>
+  <si>
     <t>Fiorino</t>
   </si>
   <si>
@@ -1304,6 +1271,12 @@
     <t xml:space="preserve">(215) 843-1500  </t>
   </si>
   <si>
+    <t>https://www.fiorino.us/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/fiorino-philadelphia-2</t>
+  </si>
+  <si>
     <t>Han dynasty (manayunk)</t>
   </si>
   <si>
@@ -1313,6 +1286,12 @@
     <t xml:space="preserve">(215) 508-2066  </t>
   </si>
   <si>
+    <t>http://www.handynasty.net/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/the-towpath-philadelphia</t>
+  </si>
+  <si>
     <t>June BYOB</t>
   </si>
   <si>
@@ -1322,6 +1301,15 @@
     <t xml:space="preserve">(856) 240-7041  </t>
   </si>
   <si>
+    <t>http://www.junebyob.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/june-byob-collingswood</t>
+  </si>
+  <si>
+    <t>info@junebyob.com</t>
+  </si>
+  <si>
     <t>Kung Fu Hot Pot</t>
   </si>
   <si>
@@ -1331,7 +1319,10 @@
     <t xml:space="preserve">(215) 606-1899  </t>
   </si>
   <si>
-    <t xml:space="preserve">(267) 928-3262  </t>
+    <t>https://www.yelp.com/biz/kungfu-hotpot-philadelphia</t>
+  </si>
+  <si>
+    <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
   </si>
   <si>
     <t>Sakartvelo</t>
@@ -1343,12 +1334,27 @@
     <t xml:space="preserve">(267) 319-1631  </t>
   </si>
   <si>
+    <t>https://sakartvelopa.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/sakartvelo-philadelphia</t>
+  </si>
+  <si>
+    <t>test@email.com</t>
+  </si>
+  <si>
     <t>Scampi</t>
   </si>
   <si>
     <t> 617 S 3rd St, Philadelphia, PA 19147 </t>
   </si>
   <si>
+    <t>https://www.scampiphilly.com/menu</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/scampi-philadelphia</t>
+  </si>
+  <si>
     <t>Vientiane Bistro</t>
   </si>
   <si>
@@ -1358,6 +1364,15 @@
     <t xml:space="preserve">(267) 703-8199  </t>
   </si>
   <si>
+    <t>https://www.vientianebistro.com/</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/vientiane-bistro-philadelphia</t>
+  </si>
+  <si>
+    <t>astigma@astigmatic.com</t>
+  </si>
+  <si>
     <t>White yak</t>
   </si>
   <si>
@@ -1367,6 +1382,12 @@
     <t xml:space="preserve">(215) 483-0764  </t>
   </si>
   <si>
+    <t>https://whiteyakrestaurant.com/?utm_source=google</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/white-yak-philadelphia</t>
+  </si>
+  <si>
     <t>Yamitsuki</t>
   </si>
   <si>
@@ -1376,6 +1397,15 @@
     <t xml:space="preserve">(215) 629-3888  </t>
   </si>
   <si>
+    <t>https://yamitsuki1028.wixsite.com/yamitsukiramen</t>
+  </si>
+  <si>
+    <t>https://www.yelp.com/biz/yamitsuki-ramen-philadelphia</t>
+  </si>
+  <si>
+    <t>yamitsuki1028@gmail.com</t>
+  </si>
+  <si>
     <t>Yanako restaurant</t>
   </si>
   <si>
@@ -1385,6 +1415,9 @@
     <t xml:space="preserve">(267) 297-8151  </t>
   </si>
   <si>
+    <t>https://theyanako.com/</t>
+  </si>
+  <si>
     <t>Zeppoli</t>
   </si>
   <si>
@@ -1394,70 +1427,16 @@
     <t xml:space="preserve">(856) 854-2670  </t>
   </si>
   <si>
-    <t>https://www.scampiphilly.com/menu</t>
-  </si>
-  <si>
-    <t>http://www.junebyob.com/</t>
-  </si>
-  <si>
     <t>http://www.zeppolirestaurant.com/</t>
   </si>
   <si>
-    <t>http://www.casablanca-grill.com/</t>
-  </si>
-  <si>
-    <t>https://www.fiorino.us/</t>
-  </si>
-  <si>
-    <t>http://www.handynasty.net/</t>
-  </si>
-  <si>
-    <t>https://whiteyakrestaurant.com/?utm_source=google</t>
-  </si>
-  <si>
-    <t>https://www.vientianebistro.com/</t>
-  </si>
-  <si>
-    <t>https://theyanako.com/</t>
-  </si>
-  <si>
-    <t>https://chabaathai.com/</t>
-  </si>
-  <si>
-    <t>http://www.apricotstonephilly.com/</t>
-  </si>
-  <si>
-    <t>https://sakartvelopa.com/</t>
-  </si>
-  <si>
-    <t>https://yamitsuki1028.wixsite.com/yamitsukiramen</t>
-  </si>
-  <si>
-    <t>info@junebyob.com</t>
-  </si>
-  <si>
-    <t>casablancamg947@gmail.com</t>
-  </si>
-  <si>
-    <t>treley@whiteyakrestaurant.com</t>
-  </si>
-  <si>
-    <t>astigma@astigmatic.com</t>
-  </si>
-  <si>
-    <t>info@apricotstonephilly.com</t>
-  </si>
-  <si>
-    <t>yamitsuki1028@gmail.com</t>
+    <t>https://www.yelp.com/biz/zeppoli-collingswood</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1521,12 +1500,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1824,12 +1811,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S90"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="21.125" customWidth="1"/>
-    <col min="9" max="9" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -1916,11 +1906,11 @@
       <c r="H2">
         <v>-75.1753073</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="2">
+        <v>45969</v>
+      </c>
+      <c r="J2" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1928,19 +1918,19 @@
         <v>1556</v>
       </c>
       <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
       </c>
       <c r="G3">
         <v>39.938799099999997</v>
@@ -1948,8 +1938,8 @@
       <c r="H3">
         <v>-75.152359599999997</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
+      <c r="I3" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -1957,19 +1947,19 @@
         <v>1557</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
       </c>
       <c r="G4">
         <v>39.950006500000001</v>
@@ -1977,8 +1967,8 @@
       <c r="H4">
         <v>-75.179640800000001</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>24</v>
+      <c r="I4" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1986,16 +1976,16 @@
         <v>1558</v>
       </c>
       <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
       </c>
       <c r="G5">
         <v>39.945162000000003</v>
@@ -2003,11 +1993,11 @@
       <c r="H5">
         <v>-75.170259099999996</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>24</v>
+      <c r="I5" s="2">
+        <v>45969</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -2015,19 +2005,19 @@
         <v>1374</v>
       </c>
       <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>44</v>
-      </c>
-      <c r="F6" t="s">
-        <v>45</v>
       </c>
       <c r="G6">
         <v>39.933934299999997</v>
@@ -2035,14 +2025,14 @@
       <c r="H6">
         <v>-75.165249199999991</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>24</v>
+      <c r="I6" s="2">
+        <v>45969</v>
       </c>
       <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
         <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -2050,19 +2040,19 @@
         <v>1559</v>
       </c>
       <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>49</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>50</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>51</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
       </c>
       <c r="G7">
         <v>39.937890799999998</v>
@@ -2070,11 +2060,11 @@
       <c r="H7">
         <v>-75.144517199999996</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>24</v>
+      <c r="I7" s="2">
+        <v>45969</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -2082,19 +2072,19 @@
         <v>1560</v>
       </c>
       <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
         <v>54</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>55</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>56</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
       </c>
       <c r="G8">
         <v>39.972437200000002</v>
@@ -2102,14 +2092,14 @@
       <c r="H8">
         <v>-75.141018599999995</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>24</v>
+      <c r="I8" s="2">
+        <v>45969</v>
       </c>
       <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
         <v>59</v>
-      </c>
-      <c r="K8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -2117,16 +2107,16 @@
         <v>1561</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>61</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>62</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>64</v>
       </c>
       <c r="G9">
         <v>39.930126299999998</v>
@@ -2134,11 +2124,11 @@
       <c r="H9">
         <v>-75.161606300000003</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
+      <c r="I9" s="2">
+        <v>45969</v>
       </c>
       <c r="J9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -2146,16 +2136,16 @@
         <v>1562</v>
       </c>
       <c r="B10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>67</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>68</v>
-      </c>
-      <c r="F10" t="s">
-        <v>69</v>
       </c>
       <c r="G10">
         <v>39.970733099999997</v>
@@ -2163,11 +2153,11 @@
       <c r="H10">
         <v>-75.129705099999995</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>24</v>
+      <c r="I10" s="2">
+        <v>45969</v>
       </c>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -2175,19 +2165,19 @@
         <v>1563</v>
       </c>
       <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>72</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>73</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>75</v>
       </c>
       <c r="G11">
         <v>39.945286199999998</v>
@@ -2195,8 +2185,8 @@
       <c r="H11">
         <v>-75.164066699999992</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>24</v>
+      <c r="I11" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -2204,19 +2194,19 @@
         <v>1564</v>
       </c>
       <c r="B12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
         <v>76</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>77</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>78</v>
       </c>
-      <c r="E12" t="s">
-        <v>79</v>
-      </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12">
         <v>39.945343899999997</v>
@@ -2224,8 +2214,8 @@
       <c r="H12">
         <v>-75.164232699999999</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>24</v>
+      <c r="I12" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2233,19 +2223,19 @@
         <v>1565</v>
       </c>
       <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" t="s">
         <v>80</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>81</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>82</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>83</v>
-      </c>
-      <c r="F13" t="s">
-        <v>84</v>
       </c>
       <c r="G13">
         <v>39.971564299999997</v>
@@ -2253,8 +2243,8 @@
       <c r="H13">
         <v>-75.144519399999993</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>24</v>
+      <c r="I13" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -2262,19 +2252,19 @@
         <v>1566</v>
       </c>
       <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
         <v>85</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>87</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>88</v>
-      </c>
-      <c r="F14" t="s">
-        <v>89</v>
       </c>
       <c r="G14">
         <v>39.967347200000013</v>
@@ -2282,11 +2272,11 @@
       <c r="H14">
         <v>-75.140985200000003</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>24</v>
+      <c r="I14" s="2">
+        <v>45969</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -2294,16 +2284,16 @@
         <v>1567</v>
       </c>
       <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
         <v>91</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>92</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>93</v>
-      </c>
-      <c r="F15" t="s">
-        <v>94</v>
       </c>
       <c r="G15">
         <v>39.944823399999997</v>
@@ -2311,11 +2301,11 @@
       <c r="H15">
         <v>-75.180016899999998</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>24</v>
+      <c r="I15" s="2">
+        <v>45969</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -2323,19 +2313,19 @@
         <v>1568</v>
       </c>
       <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
         <v>96</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>97</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>98</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" t="s">
-        <v>100</v>
       </c>
       <c r="G16">
         <v>39.944419500000002</v>
@@ -2343,8 +2333,8 @@
       <c r="H16">
         <v>-75.170737899999992</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>24</v>
+      <c r="I16" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -2352,16 +2342,16 @@
         <v>1569</v>
       </c>
       <c r="B17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" t="s">
         <v>101</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>102</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>103</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
       </c>
       <c r="G17">
         <v>39.949910799999998</v>
@@ -2369,8 +2359,8 @@
       <c r="H17">
         <v>-75.160454999999999</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>24</v>
+      <c r="I17" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -2378,19 +2368,19 @@
         <v>1570</v>
       </c>
       <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
         <v>105</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>106</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>107</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>108</v>
-      </c>
-      <c r="F18" t="s">
-        <v>109</v>
       </c>
       <c r="G18">
         <v>39.947785699999997</v>
@@ -2398,8 +2388,8 @@
       <c r="H18">
         <v>-75.160108000000008</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>24</v>
+      <c r="I18" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -2407,16 +2397,16 @@
         <v>1571</v>
       </c>
       <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
         <v>110</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>111</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>112</v>
-      </c>
-      <c r="E19" t="s">
-        <v>113</v>
       </c>
       <c r="G19">
         <v>39.9681268</v>
@@ -2424,8 +2414,8 @@
       <c r="H19">
         <v>-75.134557399999991</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>24</v>
+      <c r="I19" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -2433,19 +2423,19 @@
         <v>1377</v>
       </c>
       <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
         <v>114</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>115</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>116</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>117</v>
-      </c>
-      <c r="F20" t="s">
-        <v>118</v>
       </c>
       <c r="G20">
         <v>39.941107500000001</v>
@@ -2453,8 +2443,8 @@
       <c r="H20">
         <v>-75.146249400000002</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>24</v>
+      <c r="I20" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -2462,19 +2452,19 @@
         <v>1573</v>
       </c>
       <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
         <v>119</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>120</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>121</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>122</v>
-      </c>
-      <c r="F21" t="s">
-        <v>123</v>
       </c>
       <c r="G21">
         <v>39.947794299999998</v>
@@ -2482,8 +2472,8 @@
       <c r="H21">
         <v>-75.167785299999991</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>24</v>
+      <c r="I21" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -2491,16 +2481,16 @@
         <v>1574</v>
       </c>
       <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
         <v>124</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>125</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>126</v>
-      </c>
-      <c r="F22" t="s">
-        <v>127</v>
       </c>
       <c r="G22">
         <v>39.919627800000001</v>
@@ -2508,8 +2498,8 @@
       <c r="H22">
         <v>-75.171386099999992</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>24</v>
+      <c r="I22" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -2517,19 +2507,19 @@
         <v>1575</v>
       </c>
       <c r="B23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" t="s">
         <v>128</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>129</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>130</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>131</v>
-      </c>
-      <c r="F23" t="s">
-        <v>132</v>
       </c>
       <c r="G23">
         <v>39.939477599999996</v>
@@ -2537,8 +2527,8 @@
       <c r="H23">
         <v>-75.171194099999994</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>24</v>
+      <c r="I23" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -2546,16 +2536,16 @@
         <v>1576</v>
       </c>
       <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
         <v>133</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>134</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>135</v>
-      </c>
-      <c r="E24" t="s">
-        <v>136</v>
       </c>
       <c r="G24">
         <v>39.939990700000003</v>
@@ -2563,11 +2553,11 @@
       <c r="H24">
         <v>-75.152963700000001</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>24</v>
+      <c r="I24" s="2">
+        <v>45969</v>
       </c>
       <c r="J24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -2575,19 +2565,19 @@
         <v>1577</v>
       </c>
       <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
         <v>138</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>139</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>140</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>141</v>
-      </c>
-      <c r="F25" t="s">
-        <v>142</v>
       </c>
       <c r="G25">
         <v>39.949691500000007</v>
@@ -2595,14 +2585,14 @@
       <c r="H25">
         <v>-75.173786499999991</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>24</v>
+      <c r="I25" s="2">
+        <v>45969</v>
       </c>
       <c r="J25" t="s">
+        <v>142</v>
+      </c>
+      <c r="K25" t="s">
         <v>143</v>
-      </c>
-      <c r="K25" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -2610,16 +2600,16 @@
         <v>1578</v>
       </c>
       <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
         <v>145</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>146</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>147</v>
-      </c>
-      <c r="F26" t="s">
-        <v>148</v>
       </c>
       <c r="G26">
         <v>39.9399765</v>
@@ -2627,8 +2617,8 @@
       <c r="H26">
         <v>-75.157853799999998</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>24</v>
+      <c r="I26" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -2636,19 +2626,19 @@
         <v>1579</v>
       </c>
       <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
         <v>149</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>150</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>151</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>152</v>
-      </c>
-      <c r="F27" t="s">
-        <v>153</v>
       </c>
       <c r="G27">
         <v>39.951250900000012</v>
@@ -2656,11 +2646,11 @@
       <c r="H27">
         <v>-75.174123500000007</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>24</v>
+      <c r="I27" s="2">
+        <v>45969</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -2668,19 +2658,19 @@
         <v>1580</v>
       </c>
       <c r="B28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" t="s">
         <v>155</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>156</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>157</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>158</v>
-      </c>
-      <c r="F28" t="s">
-        <v>159</v>
       </c>
       <c r="G28">
         <v>39.946499199999998</v>
@@ -2688,14 +2678,14 @@
       <c r="H28">
         <v>-75.161768199999997</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>24</v>
+      <c r="I28" s="2">
+        <v>45969</v>
       </c>
       <c r="J28" t="s">
+        <v>159</v>
+      </c>
+      <c r="K28" t="s">
         <v>160</v>
-      </c>
-      <c r="K28" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -2703,19 +2693,19 @@
         <v>1581</v>
       </c>
       <c r="B29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" t="s">
         <v>162</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>163</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>164</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>165</v>
-      </c>
-      <c r="F29" t="s">
-        <v>166</v>
       </c>
       <c r="G29">
         <v>39.953597799999997</v>
@@ -2723,8 +2713,8 @@
       <c r="H29">
         <v>-75.160984799999994</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>24</v>
+      <c r="I29" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -2732,19 +2722,19 @@
         <v>1582</v>
       </c>
       <c r="B30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" t="s">
         <v>167</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>168</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>169</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>170</v>
-      </c>
-      <c r="F30" t="s">
-        <v>171</v>
       </c>
       <c r="G30">
         <v>39.944041200000001</v>
@@ -2752,8 +2742,8 @@
       <c r="H30">
         <v>-75.170019699999997</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>24</v>
+      <c r="I30" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -2761,19 +2751,19 @@
         <v>1583</v>
       </c>
       <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="s">
         <v>172</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>173</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>174</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>175</v>
-      </c>
-      <c r="F31" t="s">
-        <v>176</v>
       </c>
       <c r="G31">
         <v>39.951949399999997</v>
@@ -2781,11 +2771,11 @@
       <c r="H31">
         <v>-75.144386900000001</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>24</v>
+      <c r="I31" s="2">
+        <v>45969</v>
       </c>
       <c r="J31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -2793,19 +2783,19 @@
         <v>1584</v>
       </c>
       <c r="B32" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" t="s">
         <v>178</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>179</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>180</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>181</v>
-      </c>
-      <c r="F32" t="s">
-        <v>182</v>
       </c>
       <c r="G32">
         <v>39.936869300000012</v>
@@ -2813,11 +2803,11 @@
       <c r="H32">
         <v>-75.156515900000002</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>24</v>
+      <c r="I32" s="2">
+        <v>45969</v>
       </c>
       <c r="J32" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -2825,19 +2815,19 @@
         <v>1585</v>
       </c>
       <c r="B33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" t="s">
         <v>184</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>185</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>186</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>187</v>
-      </c>
-      <c r="F33" t="s">
-        <v>188</v>
       </c>
       <c r="G33">
         <v>39.965340099999999</v>
@@ -2845,11 +2835,11 @@
       <c r="H33">
         <v>-75.140709299999997</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>24</v>
+      <c r="I33" s="2">
+        <v>45969</v>
       </c>
       <c r="J33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -2857,16 +2847,16 @@
         <v>1586</v>
       </c>
       <c r="B34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" t="s">
         <v>190</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>191</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>192</v>
-      </c>
-      <c r="F34" t="s">
-        <v>193</v>
       </c>
       <c r="G34">
         <v>39.951353500000003</v>
@@ -2874,8 +2864,8 @@
       <c r="H34">
         <v>-75.175115599999998</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>24</v>
+      <c r="I34" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -2883,19 +2873,19 @@
         <v>1587</v>
       </c>
       <c r="B35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C35" t="s">
         <v>194</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>195</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>196</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>197</v>
-      </c>
-      <c r="F35" t="s">
-        <v>198</v>
       </c>
       <c r="G35">
         <v>39.926275500000003</v>
@@ -2903,68 +2893,74 @@
       <c r="H35">
         <v>-75.167463699999999</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>24</v>
+      <c r="I35" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1588</v>
+      </c>
       <c r="B36" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" t="s">
         <v>199</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>200</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>201</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>202</v>
       </c>
-      <c r="F36" t="s">
-        <v>203</v>
-      </c>
       <c r="G36">
-        <v>39.943980099999997</v>
+        <v>39.919344799999998</v>
       </c>
       <c r="H36">
-        <v>-75.16734799999999</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>24</v>
+        <v>-75.171119699999991</v>
+      </c>
+      <c r="I36" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B37" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" t="s">
         <v>204</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>205</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>206</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>207</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37">
+        <v>39.925220400000001</v>
+      </c>
+      <c r="H37">
+        <v>-75.174716699999991</v>
+      </c>
+      <c r="I37" s="2">
+        <v>45969</v>
+      </c>
+      <c r="J37" t="s">
         <v>208</v>
-      </c>
-      <c r="G37">
-        <v>39.919344799999998</v>
-      </c>
-      <c r="H37">
-        <v>-75.171119699999991</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B38" t="s">
         <v>209</v>
@@ -2982,50 +2978,50 @@
         <v>213</v>
       </c>
       <c r="G38">
-        <v>39.925220400000001</v>
+        <v>39.9339212</v>
       </c>
       <c r="H38">
-        <v>-75.174716699999991</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" t="s">
-        <v>214</v>
+        <v>-75.155556500000003</v>
+      </c>
+      <c r="I38" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" t="s">
         <v>215</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>216</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>217</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>218</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39">
+        <v>39.942576899999999</v>
+      </c>
+      <c r="H39">
+        <v>-75.185306799999992</v>
+      </c>
+      <c r="I39" s="2">
+        <v>45969</v>
+      </c>
+      <c r="J39" t="s">
         <v>219</v>
-      </c>
-      <c r="G39">
-        <v>39.9339212</v>
-      </c>
-      <c r="H39">
-        <v>-75.155556500000003</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B40" t="s">
         <v>220</v>
@@ -3043,13 +3039,13 @@
         <v>224</v>
       </c>
       <c r="G40">
-        <v>39.942576899999999</v>
+        <v>39.948765399999999</v>
       </c>
       <c r="H40">
-        <v>-75.185306799999992</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>24</v>
+        <v>-75.177968399999997</v>
+      </c>
+      <c r="I40" s="2">
+        <v>45969</v>
       </c>
       <c r="J40" t="s">
         <v>225</v>
@@ -3057,7 +3053,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B41" t="s">
         <v>226</v>
@@ -3075,82 +3071,79 @@
         <v>230</v>
       </c>
       <c r="G41">
-        <v>39.948765399999999</v>
+        <v>39.9515782</v>
       </c>
       <c r="H41">
-        <v>-75.177968399999997</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J41" t="s">
-        <v>231</v>
+        <v>-75.174830900000003</v>
+      </c>
+      <c r="I41" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B42" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" t="s">
         <v>232</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>233</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>234</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>235</v>
       </c>
-      <c r="F42" t="s">
-        <v>236</v>
-      </c>
       <c r="G42">
-        <v>39.9515782</v>
+        <v>39.948388199999997</v>
       </c>
       <c r="H42">
-        <v>-75.174830900000003</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>24</v>
+        <v>-75.217944799999998</v>
+      </c>
+      <c r="I42" s="2">
+        <v>45969</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1594</v>
+        <v>1726</v>
       </c>
       <c r="B43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C43" t="s">
         <v>237</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>238</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>239</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>240</v>
       </c>
-      <c r="F43" t="s">
-        <v>241</v>
-      </c>
       <c r="G43">
-        <v>39.948388199999997</v>
+        <v>39.931907000000002</v>
       </c>
       <c r="H43">
-        <v>-75.217944799999998</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>24</v>
+        <v>-75.149544399999996</v>
+      </c>
+      <c r="I43" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B44" t="s">
-        <v>405</v>
+        <v>241</v>
       </c>
       <c r="C44" t="s">
         <v>242</v>
@@ -3158,980 +3151,977 @@
       <c r="D44" t="s">
         <v>243</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>244</v>
       </c>
-      <c r="F44" t="s">
-        <v>245</v>
-      </c>
       <c r="G44">
-        <v>39.931907000000002</v>
+        <v>39.910426600000001</v>
       </c>
       <c r="H44">
-        <v>-75.149544399999996</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>246</v>
+        <v>-75.050069499999992</v>
+      </c>
+      <c r="I44" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B45" t="s">
+        <v>245</v>
+      </c>
+      <c r="C45" t="s">
+        <v>246</v>
+      </c>
+      <c r="D45" t="s">
         <v>247</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>248</v>
       </c>
-      <c r="D45" t="s">
+      <c r="G45">
+        <v>39.941114900000002</v>
+      </c>
+      <c r="H45">
+        <v>-75.149088399999997</v>
+      </c>
+      <c r="I45" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1730</v>
+      </c>
+      <c r="B46" t="s">
         <v>249</v>
       </c>
-      <c r="F45" t="s">
+      <c r="C46" t="s">
         <v>250</v>
       </c>
-      <c r="G45">
-        <v>39.910426600000001</v>
-      </c>
-      <c r="H45">
-        <v>-75.050069499999992</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+      <c r="D46" t="s">
         <v>251</v>
       </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
         <v>252</v>
       </c>
-      <c r="D46" t="s">
-        <v>253</v>
-      </c>
-      <c r="E46" t="s">
-        <v>254</v>
-      </c>
-      <c r="F46" t="s">
-        <v>255</v>
-      </c>
       <c r="G46">
-        <v>39.947021399999997</v>
+        <v>39.939704499999998</v>
       </c>
       <c r="H46">
-        <v>-75.154025899999993</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J46" t="s">
-        <v>256</v>
-      </c>
-      <c r="K46" t="s">
-        <v>257</v>
+        <v>-75.156259599999998</v>
+      </c>
+      <c r="I46" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D47" t="s">
-        <v>260</v>
+        <v>255</v>
+      </c>
+      <c r="E47" t="s">
+        <v>256</v>
       </c>
       <c r="F47" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G47">
-        <v>39.941114900000002</v>
+        <v>39.968518099999997</v>
       </c>
       <c r="H47">
-        <v>-75.149088399999997</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>246</v>
+        <v>-75.178519699999995</v>
+      </c>
+      <c r="I47" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="B48" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" t="s">
+        <v>259</v>
+      </c>
+      <c r="D48" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" t="s">
+        <v>261</v>
+      </c>
+      <c r="F48" t="s">
         <v>262</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48">
+        <v>39.9413883</v>
+      </c>
+      <c r="H48">
+        <v>-75.150354600000014</v>
+      </c>
+      <c r="I48" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J48" t="s">
         <v>263</v>
       </c>
-      <c r="D48" t="s">
+      <c r="K48" t="s">
         <v>264</v>
-      </c>
-      <c r="F48" t="s">
-        <v>265</v>
-      </c>
-      <c r="G48">
-        <v>39.939704499999998</v>
-      </c>
-      <c r="H48">
-        <v>-75.156259599999998</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B49" t="s">
+        <v>265</v>
+      </c>
+      <c r="C49" t="s">
         <v>266</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>267</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>268</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>269</v>
       </c>
-      <c r="F49" t="s">
-        <v>270</v>
-      </c>
       <c r="G49">
-        <v>39.968518099999997</v>
+        <v>40.1219337</v>
       </c>
       <c r="H49">
-        <v>-75.178519699999995</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>246</v>
+        <v>-75.034327399999995</v>
+      </c>
+      <c r="I49" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="B50" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>272</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>273</v>
       </c>
-      <c r="E50" t="s">
-        <v>274</v>
-      </c>
-      <c r="F50" t="s">
-        <v>275</v>
-      </c>
       <c r="G50">
-        <v>39.9413883</v>
+        <v>39.928446399999999</v>
       </c>
       <c r="H50">
-        <v>-75.150354600000014</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J50" t="s">
-        <v>276</v>
-      </c>
-      <c r="K50" t="s">
-        <v>277</v>
+        <v>-75.171258600000002</v>
+      </c>
+      <c r="I50" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="B51" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C51" t="s">
-        <v>279</v>
-      </c>
-      <c r="D51" t="s">
-        <v>280</v>
-      </c>
-      <c r="E51" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F51" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G51">
-        <v>40.1219337</v>
+        <v>39.919901199999998</v>
       </c>
       <c r="H51">
-        <v>-75.034327399999995</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>246</v>
+        <v>-75.173383200000004</v>
+      </c>
+      <c r="I51" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B52" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" t="s">
+        <v>278</v>
+      </c>
+      <c r="D52" t="s">
+        <v>279</v>
+      </c>
+      <c r="E52" t="s">
+        <v>280</v>
+      </c>
+      <c r="F52" t="s">
+        <v>281</v>
+      </c>
+      <c r="G52">
+        <v>39.9463188</v>
+      </c>
+      <c r="H52">
+        <v>-75.157960899999992</v>
+      </c>
+      <c r="I52" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J52" t="s">
+        <v>282</v>
+      </c>
+      <c r="K52" t="s">
         <v>283</v>
-      </c>
-      <c r="C52" t="s">
-        <v>284</v>
-      </c>
-      <c r="D52" t="s">
-        <v>285</v>
-      </c>
-      <c r="F52" t="s">
-        <v>286</v>
-      </c>
-      <c r="G52">
-        <v>39.928446399999999</v>
-      </c>
-      <c r="H52">
-        <v>-75.171258600000002</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="B53" t="s">
+        <v>284</v>
+      </c>
+      <c r="C53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D53" t="s">
+        <v>286</v>
+      </c>
+      <c r="E53" t="s">
         <v>287</v>
       </c>
-      <c r="C53" t="s">
+      <c r="F53" t="s">
         <v>288</v>
       </c>
-      <c r="F53" t="s">
-        <v>289</v>
-      </c>
       <c r="G53">
-        <v>39.919901199999998</v>
+        <v>39.918631400000002</v>
       </c>
       <c r="H53">
-        <v>-75.173383200000004</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>246</v>
+        <v>-75.153989299999992</v>
+      </c>
+      <c r="I53" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B54" t="s">
+        <v>289</v>
+      </c>
+      <c r="C54" t="s">
         <v>290</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>291</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>292</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>293</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54">
+        <v>39.947769000000001</v>
+      </c>
+      <c r="H54">
+        <v>-75.16970049999999</v>
+      </c>
+      <c r="I54" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J54" t="s">
         <v>294</v>
-      </c>
-      <c r="G54">
-        <v>39.9463188</v>
-      </c>
-      <c r="H54">
-        <v>-75.157960899999992</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J54" t="s">
-        <v>295</v>
-      </c>
-      <c r="K54" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B55" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" t="s">
+        <v>296</v>
+      </c>
+      <c r="D55" t="s">
         <v>297</v>
       </c>
-      <c r="C55" t="s">
+      <c r="F55" t="s">
         <v>298</v>
       </c>
-      <c r="D55" t="s">
-        <v>299</v>
-      </c>
-      <c r="E55" t="s">
-        <v>300</v>
-      </c>
-      <c r="F55" t="s">
-        <v>301</v>
-      </c>
       <c r="G55">
-        <v>39.918631400000002</v>
+        <v>39.943967499999999</v>
       </c>
       <c r="H55">
-        <v>-75.153989299999992</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>246</v>
+        <v>-75.169153299999991</v>
+      </c>
+      <c r="I55" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="B56" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" t="s">
+        <v>300</v>
+      </c>
+      <c r="D56" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56" t="s">
         <v>302</v>
       </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
         <v>303</v>
       </c>
-      <c r="D56" t="s">
+      <c r="G56">
+        <v>40.059318500000003</v>
+      </c>
+      <c r="H56">
+        <v>-75.190036300000003</v>
+      </c>
+      <c r="I56" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J56" t="s">
         <v>304</v>
       </c>
-      <c r="E56" t="s">
+      <c r="K56" t="s">
         <v>305</v>
       </c>
-      <c r="F56" t="s">
+      <c r="L56" t="s">
         <v>306</v>
-      </c>
-      <c r="G56">
-        <v>39.947769000000001</v>
-      </c>
-      <c r="H56">
-        <v>-75.16970049999999</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J56" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B57" t="s">
+        <v>307</v>
+      </c>
+      <c r="C57" t="s">
         <v>308</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>309</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>310</v>
       </c>
       <c r="F57" t="s">
         <v>311</v>
       </c>
       <c r="G57">
-        <v>39.943967499999999</v>
+        <v>39.921155900000002</v>
       </c>
       <c r="H57">
-        <v>-75.169153299999991</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>246</v>
+        <v>-75.163266499999992</v>
+      </c>
+      <c r="I57" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J57" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="B58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E58" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F58" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G58">
-        <v>40.059318500000003</v>
+        <v>39.926405699999997</v>
       </c>
       <c r="H58">
-        <v>-75.190036300000003</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J58" t="s">
-        <v>317</v>
-      </c>
-      <c r="K58" t="s">
-        <v>318</v>
-      </c>
-      <c r="L58" t="s">
-        <v>319</v>
+        <v>-75.157535600000003</v>
+      </c>
+      <c r="I58" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B59" t="s">
+        <v>318</v>
+      </c>
+      <c r="C59" t="s">
+        <v>319</v>
+      </c>
+      <c r="D59" t="s">
         <v>320</v>
       </c>
-      <c r="C59" t="s">
+      <c r="E59" t="s">
         <v>321</v>
       </c>
-      <c r="D59" t="s">
+      <c r="F59" t="s">
         <v>322</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59">
+        <v>39.952112100000001</v>
+      </c>
+      <c r="H59">
+        <v>-75.172149099999999</v>
+      </c>
+      <c r="I59" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J59" t="s">
         <v>323</v>
-      </c>
-      <c r="F59" t="s">
-        <v>324</v>
-      </c>
-      <c r="G59">
-        <v>39.921155900000002</v>
-      </c>
-      <c r="H59">
-        <v>-75.163266499999992</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J59" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="B60" t="s">
+        <v>324</v>
+      </c>
+      <c r="C60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D60" t="s">
         <v>326</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
         <v>327</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>328</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60">
+        <v>39.982485199999999</v>
+      </c>
+      <c r="H60">
+        <v>-75.102839599999996</v>
+      </c>
+      <c r="I60" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J60" t="s">
         <v>329</v>
-      </c>
-      <c r="F60" t="s">
-        <v>330</v>
-      </c>
-      <c r="G60">
-        <v>39.926405699999997</v>
-      </c>
-      <c r="H60">
-        <v>-75.157535600000003</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B61" t="s">
+        <v>330</v>
+      </c>
+      <c r="C61" t="s">
         <v>331</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>332</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>333</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>334</v>
       </c>
-      <c r="F61" t="s">
-        <v>335</v>
-      </c>
       <c r="G61">
-        <v>39.952112100000001</v>
+        <v>39.940707699999997</v>
       </c>
       <c r="H61">
-        <v>-75.172149099999999</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J61" t="s">
-        <v>336</v>
+        <v>-75.146044199999992</v>
+      </c>
+      <c r="I61" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="B62" t="s">
+        <v>335</v>
+      </c>
+      <c r="C62" t="s">
+        <v>336</v>
+      </c>
+      <c r="D62" t="s">
         <v>337</v>
       </c>
-      <c r="C62" t="s">
+      <c r="E62" t="s">
         <v>338</v>
       </c>
-      <c r="D62" t="s">
+      <c r="F62" t="s">
         <v>339</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62">
+        <v>39.938333399999998</v>
+      </c>
+      <c r="H62">
+        <v>-75.159783899999994</v>
+      </c>
+      <c r="I62" s="2">
+        <v>45977</v>
+      </c>
+      <c r="J62" t="s">
         <v>340</v>
       </c>
-      <c r="F62" t="s">
+      <c r="K62" t="s">
         <v>341</v>
-      </c>
-      <c r="G62">
-        <v>39.982485199999999</v>
-      </c>
-      <c r="H62">
-        <v>-75.102839599999996</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J62" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B63" t="s">
+        <v>342</v>
+      </c>
+      <c r="C63" t="s">
         <v>343</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>344</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>345</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>346</v>
       </c>
-      <c r="F63" t="s">
-        <v>347</v>
-      </c>
       <c r="G63">
-        <v>39.940707699999997</v>
+        <v>39.9803949</v>
       </c>
       <c r="H63">
-        <v>-75.146044199999992</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>246</v>
+        <v>-75.113133699999992</v>
+      </c>
+      <c r="I63" s="2">
+        <v>45977</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B64" t="s">
+        <v>347</v>
+      </c>
+      <c r="C64" t="s">
         <v>348</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>349</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>350</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>351</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64">
+        <v>39.926336599999999</v>
+      </c>
+      <c r="H64">
+        <v>-75.147412399999993</v>
+      </c>
+      <c r="I64" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1749</v>
+      </c>
+      <c r="B65" t="s">
         <v>352</v>
       </c>
-      <c r="G64">
-        <v>39.938333399999998</v>
-      </c>
-      <c r="H64">
-        <v>-75.159783899999994</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="J64" t="s">
+      <c r="C65" t="s">
         <v>353</v>
       </c>
-      <c r="K64" t="s">
+      <c r="D65" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>1747</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="E65" t="s">
         <v>355</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>356</v>
       </c>
-      <c r="D65" t="s">
+      <c r="G65">
+        <v>39.964689399999997</v>
+      </c>
+      <c r="H65">
+        <v>-75.174111199999999</v>
+      </c>
+      <c r="I65" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1750</v>
+      </c>
+      <c r="B66" t="s">
         <v>357</v>
       </c>
-      <c r="E65" t="s">
+      <c r="C66" t="s">
         <v>358</v>
       </c>
-      <c r="F65" t="s">
+      <c r="D66" t="s">
         <v>359</v>
       </c>
-      <c r="G65">
-        <v>39.9803949</v>
-      </c>
-      <c r="H65">
-        <v>-75.113133699999992</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>1748</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="E66" t="s">
         <v>360</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
         <v>361</v>
       </c>
-      <c r="D66" t="s">
+      <c r="G66">
+        <v>39.947806000000007</v>
+      </c>
+      <c r="H66">
+        <v>-75.160342099999994</v>
+      </c>
+      <c r="I66" s="2">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1754</v>
+      </c>
+      <c r="B67" t="s">
         <v>362</v>
       </c>
-      <c r="E66" t="s">
+      <c r="C67" t="s">
         <v>363</v>
       </c>
-      <c r="F66" t="s">
+      <c r="D67" t="s">
         <v>364</v>
       </c>
-      <c r="G66">
-        <v>39.926336599999999</v>
-      </c>
-      <c r="H66">
-        <v>-75.147412399999993</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>1749</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="E67" t="s">
         <v>365</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
         <v>366</v>
       </c>
-      <c r="D67" t="s">
+      <c r="G67">
+        <v>39.944972700000001</v>
+      </c>
+      <c r="H67">
+        <v>-75.177395099999998</v>
+      </c>
+      <c r="I67" s="2">
+        <v>45978</v>
+      </c>
+      <c r="J67" t="s">
         <v>367</v>
       </c>
-      <c r="E67" t="s">
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1755</v>
+      </c>
+      <c r="B68" t="s">
         <v>368</v>
       </c>
-      <c r="F67" t="s">
+      <c r="C68" t="s">
         <v>369</v>
       </c>
-      <c r="G67">
-        <v>39.964689399999997</v>
-      </c>
-      <c r="H67">
-        <v>-75.174111199999999</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>1750</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="E68" t="s">
         <v>370</v>
       </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
         <v>371</v>
       </c>
-      <c r="D68" t="s">
+      <c r="G68">
+        <v>39.974236699999999</v>
+      </c>
+      <c r="H68">
+        <v>-75.182546800000011</v>
+      </c>
+      <c r="I68" s="2">
+        <v>45978</v>
+      </c>
+      <c r="J68" t="s">
         <v>372</v>
       </c>
-      <c r="E68" t="s">
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1756</v>
+      </c>
+      <c r="B69" t="s">
         <v>373</v>
       </c>
-      <c r="F68" t="s">
+      <c r="C69" t="s">
         <v>374</v>
       </c>
-      <c r="G68">
-        <v>39.947806000000007</v>
-      </c>
-      <c r="H68">
-        <v>-75.160342099999994</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>1754</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
         <v>375</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" t="s">
         <v>376</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>377</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69">
+        <v>39.9798258</v>
+      </c>
+      <c r="H69">
+        <v>-75.129835499999999</v>
+      </c>
+      <c r="I69" s="2">
+        <v>45978</v>
+      </c>
+      <c r="J69" t="s">
         <v>378</v>
       </c>
-      <c r="F69" t="s">
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1757</v>
+      </c>
+      <c r="B70" t="s">
         <v>379</v>
       </c>
-      <c r="G69">
-        <v>39.944972700000001</v>
-      </c>
-      <c r="H69">
-        <v>-75.177395099999998</v>
-      </c>
-      <c r="I69" s="2" t="s">
+      <c r="C70" t="s">
         <v>380</v>
       </c>
-      <c r="J69" t="s">
+      <c r="D70" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>1755</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="E70" t="s">
         <v>382</v>
       </c>
-      <c r="C70" t="s">
+      <c r="F70" t="s">
         <v>383</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70">
+        <v>39.944876200000003</v>
+      </c>
+      <c r="H70">
+        <v>-75.160762800000001</v>
+      </c>
+      <c r="I70" s="2">
+        <v>45979</v>
+      </c>
+      <c r="J70" t="s">
         <v>384</v>
       </c>
-      <c r="F70" t="s">
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1402</v>
+      </c>
+      <c r="B71" t="s">
         <v>385</v>
       </c>
-      <c r="G70">
-        <v>39.974236699999999</v>
-      </c>
-      <c r="H70">
-        <v>-75.182546800000011</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="J70" t="s">
+      <c r="C71" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>1756</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>387</v>
       </c>
-      <c r="C71" t="s">
+      <c r="E71" t="s">
         <v>388</v>
       </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
         <v>389</v>
       </c>
-      <c r="E71" t="s">
+      <c r="G71">
+        <v>39.939035199999999</v>
+      </c>
+      <c r="H71">
+        <v>-75.159225399999997</v>
+      </c>
+      <c r="I71" s="2">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>1408</v>
+      </c>
+      <c r="B72" t="s">
         <v>390</v>
       </c>
-      <c r="F71" t="s">
+      <c r="C72" t="s">
         <v>391</v>
       </c>
-      <c r="G71">
-        <v>39.9798258</v>
-      </c>
-      <c r="H71">
-        <v>-75.129835499999999</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="J71" t="s">
+      <c r="D72" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>1757</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="G72">
+        <v>39.941414799999997</v>
+      </c>
+      <c r="H72">
+        <v>-75.149054199999995</v>
+      </c>
+      <c r="I72" s="2">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>1389</v>
+      </c>
+      <c r="B73" t="s">
         <v>393</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>394</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D73" t="s">
         <v>395</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E73" t="s">
         <v>396</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F73" t="s">
         <v>397</v>
       </c>
-      <c r="G72">
-        <v>39.944876200000003</v>
-      </c>
-      <c r="H72">
-        <v>-75.160762800000001</v>
-      </c>
-      <c r="I72" s="2" t="s">
+      <c r="G73">
+        <v>39.969888599999997</v>
+      </c>
+      <c r="H73">
+        <v>-75.144038499999994</v>
+      </c>
+      <c r="I73" s="2">
+        <v>45987</v>
+      </c>
+      <c r="J73" t="s">
         <v>398</v>
       </c>
-      <c r="J72" t="s">
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>1407</v>
+      </c>
+      <c r="B74" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>1402</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="C74" t="s">
         <v>400</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D74" t="s">
         <v>401</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E74" t="s">
         <v>402</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F74" t="s">
         <v>403</v>
       </c>
-      <c r="F73" t="s">
-        <v>404</v>
-      </c>
-      <c r="G73">
-        <v>39.939035199999999</v>
-      </c>
-      <c r="H73">
-        <v>-75.159225399999997</v>
-      </c>
-      <c r="I73" s="2">
-        <v>45985</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>1408</v>
-      </c>
-      <c r="B74" t="s">
-        <v>406</v>
-      </c>
-      <c r="C74" t="s">
-        <v>407</v>
-      </c>
-      <c r="D74" t="s">
-        <v>408</v>
-      </c>
       <c r="G74">
-        <v>39.941414799999997</v>
+        <v>39.9346672</v>
       </c>
       <c r="H74">
-        <v>-75.149054199999995</v>
+        <v>-75.160286099999993</v>
       </c>
       <c r="I74" s="2">
         <v>45987</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J74" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="B75" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C75" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D75" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E75" t="s">
-        <v>463</v>
+        <v>408</v>
       </c>
       <c r="G75">
-        <v>39.969888599999997</v>
+        <v>40.025693400000002</v>
       </c>
       <c r="H75">
-        <v>-75.144038499999994</v>
+        <v>-75.2233971</v>
       </c>
       <c r="I75" s="2">
         <v>45987</v>
       </c>
-      <c r="J75" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>409</v>
       </c>
       <c r="C76" t="s">
+        <v>410</v>
+      </c>
+      <c r="D76" t="s">
+        <v>411</v>
+      </c>
+      <c r="E76" t="s">
         <v>412</v>
       </c>
-      <c r="D76" t="s">
+      <c r="F76" t="s">
         <v>413</v>
       </c>
-      <c r="E76" t="s">
-        <v>44</v>
-      </c>
       <c r="G76">
-        <v>39.933934299999997</v>
+        <v>40.009791999999997</v>
       </c>
       <c r="H76">
-        <v>-75.165249199999991</v>
+        <v>-75.190426099999996</v>
       </c>
       <c r="I76" s="2">
         <v>45987</v>
       </c>
-      <c r="J76" t="s">
-        <v>47</v>
-      </c>
-      <c r="K76" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B77" t="s">
         <v>414</v>
@@ -4143,367 +4133,295 @@
         <v>416</v>
       </c>
       <c r="E77" t="s">
-        <v>456</v>
+        <v>417</v>
+      </c>
+      <c r="F77" t="s">
+        <v>418</v>
       </c>
       <c r="G77">
-        <v>39.9346672</v>
+        <v>40.025373700000003</v>
       </c>
       <c r="H77">
-        <v>-75.160286099999993</v>
+        <v>-75.223862799999992</v>
       </c>
       <c r="I77" s="2">
         <v>45987</v>
       </c>
-      <c r="J77" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="B78" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C78" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D78" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E78" t="s">
-        <v>462</v>
+        <v>422</v>
+      </c>
+      <c r="F78" t="s">
+        <v>423</v>
       </c>
       <c r="G78">
-        <v>40.025693400000002</v>
+        <v>39.916215800000003</v>
       </c>
       <c r="H78">
-        <v>-75.2233971</v>
+        <v>-75.069438599999998</v>
       </c>
       <c r="I78" s="2">
         <v>45987</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J78" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1401</v>
+        <v>1417</v>
       </c>
       <c r="B79" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C79" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D79" t="s">
-        <v>422</v>
-      </c>
-      <c r="E79" t="s">
-        <v>457</v>
+        <v>427</v>
+      </c>
+      <c r="F79" t="s">
+        <v>428</v>
       </c>
       <c r="G79">
-        <v>40.009791999999997</v>
+        <v>39.954462199999988</v>
       </c>
       <c r="H79">
-        <v>-75.190426099999996</v>
+        <v>-75.156541500000003</v>
       </c>
       <c r="I79" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1404</v>
+        <v>1388</v>
       </c>
       <c r="B80" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D80" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E80" t="s">
-        <v>458</v>
+        <v>433</v>
+      </c>
+      <c r="F80" t="s">
+        <v>434</v>
       </c>
       <c r="G80">
-        <v>40.025373700000003</v>
+        <v>39.949672</v>
       </c>
       <c r="H80">
-        <v>-75.223862799999992</v>
+        <v>-75.152562000000017</v>
       </c>
       <c r="I80" s="2">
         <v>45987</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J80" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B81" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C81" t="s">
-        <v>427</v>
-      </c>
-      <c r="D81" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E81" t="s">
-        <v>454</v>
+        <v>438</v>
+      </c>
+      <c r="F81" t="s">
+        <v>439</v>
       </c>
       <c r="G81">
-        <v>39.916215800000003</v>
+        <v>39.940898199999999</v>
       </c>
       <c r="H81">
-        <v>-75.069438599999998</v>
+        <v>-75.147503599999993</v>
       </c>
       <c r="I81" s="2">
         <v>45987</v>
       </c>
-      <c r="J81" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>1417</v>
+        <v>1383</v>
       </c>
       <c r="B82" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="C82" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="D82" t="s">
-        <v>431</v>
+        <v>442</v>
+      </c>
+      <c r="E82" t="s">
+        <v>443</v>
+      </c>
+      <c r="F82" t="s">
+        <v>444</v>
       </c>
       <c r="G82">
-        <v>39.954462199999988</v>
+        <v>39.988109899999998</v>
       </c>
       <c r="H82">
-        <v>-75.156541500000003</v>
+        <v>-75.1282341</v>
       </c>
       <c r="I82" s="2">
         <v>45987</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>446</v>
       </c>
       <c r="C83" t="s">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="D83" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="E83" t="s">
-        <v>117</v>
+        <v>449</v>
+      </c>
+      <c r="F83" t="s">
+        <v>450</v>
       </c>
       <c r="G83">
-        <v>39.941107500000001</v>
+        <v>40.033780200000002</v>
       </c>
       <c r="H83">
-        <v>-75.146249400000002</v>
+        <v>-75.21579659999999</v>
       </c>
       <c r="I83" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B84" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C84" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D84" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E84" t="s">
-        <v>464</v>
+        <v>454</v>
+      </c>
+      <c r="F84" t="s">
+        <v>455</v>
       </c>
       <c r="G84">
-        <v>39.949672</v>
+        <v>39.953542300000002</v>
       </c>
       <c r="H84">
-        <v>-75.152562000000017</v>
+        <v>-75.157455200000001</v>
       </c>
       <c r="I84" s="2">
         <v>45987</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J84" t="s">
+        <v>429</v>
+      </c>
+      <c r="K84" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1412</v>
+        <v>1399</v>
       </c>
       <c r="B85" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C85" t="s">
-        <v>437</v>
+        <v>458</v>
+      </c>
+      <c r="D85" t="s">
+        <v>459</v>
       </c>
       <c r="E85" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G85">
-        <v>39.940898199999999</v>
+        <v>40.025600900000001</v>
       </c>
       <c r="H85">
-        <v>-75.147503599999993</v>
+        <v>-75.2234981</v>
       </c>
       <c r="I85" s="2">
         <v>45987</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1383</v>
+        <v>1409</v>
       </c>
       <c r="B86" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C86" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="D86" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="E86" t="s">
-        <v>460</v>
+        <v>464</v>
+      </c>
+      <c r="F86" t="s">
+        <v>465</v>
       </c>
       <c r="G86">
-        <v>39.988109899999998</v>
+        <v>39.910713899999998</v>
       </c>
       <c r="H86">
-        <v>-75.1282341</v>
+        <v>-75.084474200000002</v>
       </c>
       <c r="I86" s="2">
         <v>45987</v>
       </c>
-      <c r="J86" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>1376</v>
-      </c>
-      <c r="B87" t="s">
-        <v>441</v>
-      </c>
-      <c r="C87" t="s">
-        <v>442</v>
-      </c>
-      <c r="D87" t="s">
-        <v>443</v>
-      </c>
-      <c r="E87" t="s">
-        <v>459</v>
-      </c>
-      <c r="G87">
-        <v>40.033780200000002</v>
-      </c>
-      <c r="H87">
-        <v>-75.21579659999999</v>
-      </c>
-      <c r="I87" s="2">
-        <v>45987</v>
-      </c>
-      <c r="J87" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>1387</v>
-      </c>
-      <c r="B88" t="s">
-        <v>444</v>
-      </c>
-      <c r="C88" t="s">
-        <v>445</v>
-      </c>
-      <c r="D88" t="s">
-        <v>446</v>
-      </c>
-      <c r="E88" t="s">
-        <v>465</v>
-      </c>
-      <c r="G88">
-        <v>39.953542300000002</v>
-      </c>
-      <c r="H88">
-        <v>-75.157455200000001</v>
-      </c>
-      <c r="I88" s="2">
-        <v>45987</v>
-      </c>
-      <c r="J88" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>1399</v>
-      </c>
-      <c r="B89" t="s">
-        <v>447</v>
-      </c>
-      <c r="C89" t="s">
-        <v>448</v>
-      </c>
-      <c r="D89" t="s">
-        <v>449</v>
-      </c>
-      <c r="E89" t="s">
-        <v>461</v>
-      </c>
-      <c r="G89">
-        <v>40.025600900000001</v>
-      </c>
-      <c r="H89">
-        <v>-75.2234981</v>
-      </c>
-      <c r="I89" s="2">
-        <v>45987</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>1409</v>
-      </c>
-      <c r="B90" t="s">
-        <v>450</v>
-      </c>
-      <c r="C90" t="s">
-        <v>451</v>
-      </c>
-      <c r="D90" t="s">
-        <v>452</v>
-      </c>
-      <c r="E90" t="s">
-        <v>455</v>
-      </c>
-      <c r="G90">
-        <v>39.910713899999998</v>
-      </c>
-      <c r="H90">
-        <v>-75.084474200000002</v>
-      </c>
-      <c r="I90" s="2">
-        <v>45987</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="N86">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>"   =COUNTIF($A$2:$A$88,$A2)&gt;1"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>